--- a/GEV.xlsx
+++ b/GEV.xlsx
@@ -1,158 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dillonwalton/Desktop/business/models/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65633015-97B6-3E47-B244-99553D7A181B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="15040" yWindow="1380" windowWidth="17820" windowHeight="16440" activeTab="1" xr2:uid="{F15DAF5B-3C17-D94B-A6BD-B495392D8E58}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15040" yWindow="1380" windowWidth="17820" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name=" Main" sheetId="1" r:id="rId1"/>
-    <sheet name="Model" sheetId="2" r:id="rId2"/>
+    <sheet name=" Main" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Model" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>S/O</t>
-  </si>
-  <si>
-    <t>Mkt Cap</t>
-  </si>
-  <si>
-    <t>Cash</t>
-  </si>
-  <si>
-    <t>Debt</t>
-  </si>
-  <si>
-    <t>EV</t>
-  </si>
-  <si>
-    <t>Main</t>
-  </si>
-  <si>
-    <t>Revenue</t>
-  </si>
-  <si>
-    <t>COGS</t>
-  </si>
-  <si>
-    <t>Operating Expenses</t>
-  </si>
-  <si>
-    <t>Q124</t>
-  </si>
-  <si>
-    <t>Q224</t>
-  </si>
-  <si>
-    <t>Q324</t>
-  </si>
-  <si>
-    <t>Q125</t>
-  </si>
-  <si>
-    <t>Q225</t>
-  </si>
-  <si>
-    <t>Q325</t>
-  </si>
-  <si>
-    <t>Q425</t>
-  </si>
-  <si>
-    <t>Q126</t>
-  </si>
-  <si>
-    <t>Q226</t>
-  </si>
-  <si>
-    <t>Q326</t>
-  </si>
-  <si>
-    <t>Q426</t>
-  </si>
-  <si>
-    <t>Q127</t>
-  </si>
-  <si>
-    <t>Q227</t>
-  </si>
-  <si>
-    <t>Q327</t>
-  </si>
-  <si>
-    <t>Q427</t>
-  </si>
-  <si>
-    <t>Cambridge, MA</t>
-  </si>
-  <si>
-    <t>Orders</t>
-  </si>
-  <si>
-    <t>Power and Electrification</t>
-  </si>
-  <si>
-    <t>Backlog</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <u val="single"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="FF0563C1"/>
+      <sz val="12"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -169,29 +59,89 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -511,63 +461,87 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14DF8E07-1958-8840-BC9E-40AE002DA6FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B3:L8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
   <cols>
-    <col min="11" max="11" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col width="11.1640625" bestFit="1" customWidth="1" style="4" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3">
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>956.85</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="J4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2">
-        <v>266333.58100000001</v>
-      </c>
-      <c r="L4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="J5" t="s">
-        <v>2</v>
+    <row r="4">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>S/O</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>266333.581</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Q226</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Mkt Cap</t>
+        </is>
       </c>
       <c r="K5" s="3">
         <f>K4*K3</f>
-        <v>254841286.97985002</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="J6" t="s">
-        <v>3</v>
-      </c>
-      <c r="L6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="J7" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="J8" t="s">
-        <v>5</v>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Q226</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Q226</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -576,103 +550,160 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FD81720-1613-0244-8F24-A38CB16996A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
   <cols>
-    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col width="17.1640625" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Q124</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Q224</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Q324</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Q125</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Q225</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Q325</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Q425</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Q126</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Q226</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Q326</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Q426</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Q127</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Q227</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Q327</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Q427</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Power and Electrification</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" s="4">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" s="4"/>
+    <row r="10" s="4">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" s="4"/>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="K13">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>9</v>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" location="' Main'!A1" display="' Main'!A1" xr:uid="{9DE7C47E-1749-644C-BC68-42AAD829F81B}"/>
+    <hyperlink ref="A1" location="' Main'!A1" display="' Main'!A1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GEV.xlsx
+++ b/GEV.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -37,6 +37,12 @@
       <name val="Aptos Narrow"/>
       <color rgb="FF0563C1"/>
       <sz val="12"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="FF595959"/>
+      <sz val="9"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -61,13 +67,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -143,6 +150,54 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -467,7 +522,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B3:L8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="11.1640625" bestFit="1" customWidth="1" style="4" min="11" max="11"/>
   </cols>
@@ -556,7 +611,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="17.1640625" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
   </cols>
@@ -567,6 +622,51 @@
           <t>Main</t>
         </is>
       </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>10-Q</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="C2" s="5" t="inlineStr">
@@ -695,16 +795,26 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="' Main'!A1" display="' Main'!A1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G1" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H1" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I1" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K1" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
 </worksheet>
 </file>